--- a/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,27</t>
+          <t>0,0; 49,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,66</t>
+          <t>0,0; 80,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 44,77</t>
+          <t>7,68; 45,65</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,68</t>
+          <t>0,0; 48,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,15</t>
+          <t>0,0; 28,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,44</t>
+          <t>0,0; 68,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,37</t>
+          <t>0,0; 31,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,22</t>
+          <t>0,0; 24,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 32,27</t>
+          <t>3,44; 30,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,07</t>
+          <t>0,0; 22,85</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,75</t>
+          <t>0,0; 44,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,19</t>
+          <t>0,0; 32,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 28,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,36</t>
+          <t>0,0; 20,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,53</t>
+          <t>0,0; 26,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,27</t>
+          <t>0,0; 19,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,05</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 28,08</t>
+          <t>3,42; 28,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,51</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 10,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 18,72</t>
+          <t>2,97; 17,21</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 28,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,8</t>
+          <t>0,0; 56,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,83</t>
+          <t>0,0; 30,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,16</t>
+          <t>0,0; 20,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,45</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,61</t>
+          <t>1,71; 12,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,2</t>
+          <t>1,47; 12,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,86</t>
+          <t>2,47; 15,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,57</t>
+          <t>2,91; 16,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,26</t>
+          <t>1,58; 9,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,23</t>
+          <t>1,79; 8,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 11,81</t>
+          <t>3,45; 11,76</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4771</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3185</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1044; 6205</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3460</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3800</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3101</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>609; 5421</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3052</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2531</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3164</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3146</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3648</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4106</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4662</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>577; 4787</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4036</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4054</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1111; 6442</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1484</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3465</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3410</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3785</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4292</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4433</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3576</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6582</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4368</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4212</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>904; 6648</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685; 5818</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1450; 8939</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1338; 7656</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1393; 8209</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2138; 10219</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3407; 11610</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,64</t>
+          <t>0,0; 49,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 45,65</t>
+          <t>4,84; 46,26</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,06</t>
+          <t>0,0; 47,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,51</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,03</t>
+          <t>0,0; 69,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,95</t>
+          <t>0,0; 38,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,62</t>
+          <t>0,0; 25,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 30,59</t>
+          <t>3,51; 29,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,85</t>
+          <t>0,0; 20,88</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,44</t>
+          <t>0,0; 54,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,29</t>
+          <t>0,0; 34,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,17</t>
+          <t>0,0; 34,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,44</t>
+          <t>0,0; 20,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,38</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,98</t>
+          <t>0,0; 19,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 21,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 28,36</t>
+          <t>3,38; 29,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,14</t>
+          <t>0,0; 11,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 17,21</t>
+          <t>2,47; 17,21</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,66</t>
+          <t>0,0; 28,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,73</t>
+          <t>0,0; 59,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,41</t>
+          <t>0,0; 32,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,15</t>
+          <t>0,0; 32,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,43</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 12,59</t>
+          <t>1,26; 13,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,46</t>
+          <t>1,47; 11,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 15,24</t>
+          <t>2,61; 14,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,66</t>
+          <t>2,78; 16,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,31</t>
+          <t>1,5; 9,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,56</t>
+          <t>1,96; 8,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,76</t>
+          <t>3,56; 12,31</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por contusión, lesión o heridas (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4771</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1044; 6205</t>
+          <t>658; 6287</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3143</t>
+          <t>0; 3111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3460</t>
+          <t>0; 3567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1822,27 +1822,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 3878</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2792</t>
+          <t>0; 3386</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3101</t>
+          <t>0; 3251</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>609; 5421</t>
+          <t>622; 5242</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3007</t>
+          <t>0; 2749</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>0; 2723</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3164</t>
+          <t>0; 3839</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3146</t>
+          <t>0; 3180</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3648</t>
+          <t>0; 3113</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4662</t>
+          <t>0; 4889</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>577; 4787</t>
+          <t>570; 4914</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 3832</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4054</t>
+          <t>0; 4667</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1111; 6442</t>
+          <t>924; 6443</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3465</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>0; 3550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>0; 3161</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4292</t>
+          <t>0; 4556</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 4486</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4368</t>
+          <t>0; 4819</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4212</t>
+          <t>0; 4146</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>904; 6648</t>
+          <t>667; 6864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>685; 5818</t>
+          <t>686; 5499</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1450; 8939</t>
+          <t>1529; 8579</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1338; 7656</t>
+          <t>1276; 7557</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1393; 8209</t>
+          <t>1325; 8045</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2138; 10219</t>
+          <t>2338; 9980</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3407; 11610</t>
+          <t>3519; 12151</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$herida-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,22 +635,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>29,52%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>17,74%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,28</t>
+          <t>0,0; 79,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,03</t>
+          <t>0,0; 48,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 46,26</t>
+          <t>4,95; 44,77</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,39</t>
+          <t>0,0; 67,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 31,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,43</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,81</t>
+          <t>0,0; 27,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 29,58</t>
+          <t>3,52; 32,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,88</t>
+          <t>0,0; 30,07</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,18</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,66</t>
+          <t>0,0; 20,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,66</t>
+          <t>3,37; 28,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 29,12</t>
+          <t>0,0; 17,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,68</t>
+          <t>0,0; 9,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 17,21</t>
+          <t>2,9; 18,72</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1065,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,77%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 65,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,99</t>
+          <t>0,0; 32,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,91</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,0</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 21,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,35%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>1,44; 12,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>2,17; 13,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,0</t>
+          <t>2,89; 16,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,77</t>
+          <t>0,0; 11,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 14,63</t>
+          <t>0,0; 7,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 16,45</t>
+          <t>1,73; 13,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,12</t>
+          <t>1,49; 8,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,36</t>
+          <t>1,87; 8,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,31</t>
+          <t>3,29; 11,81</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>1705</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 3171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3185</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>658; 6287</t>
+          <t>673; 6085</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3111</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2742</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3183</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3878</t>
+          <t>0; 2810</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3386</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 3429</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>622; 5242</t>
+          <t>624; 5718</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2749</t>
+          <t>0; 3957</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>802</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3724</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2723</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3839</t>
+          <t>0; 3492</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>0; 3132</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>777</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1119</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3113</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>569; 4739</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>570; 4914</t>
+          <t>0; 3550</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3832</t>
+          <t>0; 4228</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 3858</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>924; 6443</t>
+          <t>1086; 7007</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>697</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3956</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3109</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3550</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3161</t>
+          <t>0; 3516</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 4247</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2824</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4819</t>
+          <t>674; 5700</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4146</t>
+          <t>1275; 8125</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>667; 6864</t>
+          <t>1328; 7613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>686; 5499</t>
+          <t>0; 4748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1529; 8579</t>
+          <t>0; 4615</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1276; 7557</t>
+          <t>914; 7185</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1325; 8045</t>
+          <t>1313; 7281</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2338; 9980</t>
+          <t>2229; 9819</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3519; 12151</t>
+          <t>3249; 11660</t>
         </is>
       </c>
     </row>
